--- a/research_materials/07_deployment/deployment.xlsx
+++ b/research_materials/07_deployment/deployment.xlsx
@@ -464,7 +464,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 21:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>

--- a/research_materials/07_deployment/deployment.xlsx
+++ b/research_materials/07_deployment/deployment.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="deployment" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="backend_stats" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="missing_variants" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="matching_base_variants" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="missing_variants" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +465,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -484,7 +485,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sheets: deployment, backend_stats, missing_variants</t>
+          <t>Sheets: deployment, backend_stats, matching_base_variants, missing_variants</t>
         </is>
       </c>
     </row>
@@ -1471,6 +1472,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(no data available yet)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/research_materials/07_deployment/deployment.xlsx
+++ b/research_materials/07_deployment/deployment.xlsx
@@ -465,7 +465,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -1472,14 +1472,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="41" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="41" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>(no data available yet)</t>
-        </is>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>size_gb</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>quant_minutes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>weights_vram_gb</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tokens_per_s</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>adapter_epoch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>judge_exact</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>judge_exact_adapter_on_training_base</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>judge_reworded</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>judge_reworded_adapter_on_training_base</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>judge_in-domain</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>judge_in-domain_adapter_on_training_base</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>judge_held-out</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>judge_held-out_adapter_on_training_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__awq_ep3__mb</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AWQ W4A16 asym (group 128)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1603.6</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>NF4-dequantized (training base)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.431</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>gemma-4-e4b-it__awq_ep3__mb</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RTN W4A16 asym (AWQ failed: ValueError)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2327.7</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>NF4-dequantized (training base)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.449</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__awq_ep2__mb</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>AWQ W4A16 asym (group 128)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1859.3</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>NF4-dequantized (training base)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.452</v>
       </c>
     </row>
   </sheetData>
@@ -1543,12 +1810,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>see results/regen/STATUS.md</t>
+          <t>see sheet matching_base_variants</t>
         </is>
       </c>
     </row>

--- a/research_materials/07_deployment/deployment.xlsx
+++ b/research_materials/07_deployment/deployment.xlsx
@@ -465,7 +465,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:58 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
